--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-16T16:45:26+05:30</t>
+    <t>2026-05-17T00:25:02+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -346,10 +346,10 @@
 </t>
   </si>
   <si>
-    <t>Starting time with UTC normalization and precision support</t>
-  </si>
-  <si>
-    <t>Starting time for the period.
+    <t>Starting time with UTC normalization, precision support and inclusive boundary</t>
+  </si>
+  <si>
+    <t>The start of the period. The boundary is inclusive.
 All timestamps SHALL be represented in UTC.
 Additional extensions may be used to indicate
 usable precision or approximate values.</t>
@@ -375,10 +375,12 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>Ending time with UTC normalization and precision support</t>
-  </si>
-  <si>
-    <t>End time for the period.
+    <t>Ending time with UTC normalization, precision support and inclusive boundary</t>
+  </si>
+  <si>
+    <t>The end of the period.  The boundary is inclusive. If the end of the period is missing, it 
+means no end was known or planned at the time the instance was created. The start may be in 
+the past, and the end date in the future, which means that period is expected/planned to end at that time.
 All timestamps SHALL be represented in UTC.
 Additional extensions may be used to indicate
 usable precision or approximate values.</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-17T00:25:02+05:30</t>
+    <t>2026-05-19T06:46:39+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T06:46:39+05:30</t>
+    <t>2026-05-19T11:54:54+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T11:54:54+05:30</t>
+    <t>2026-05-25T12:07:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:07:44+05:30</t>
+    <t>2026-05-25T12:34:12+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T12:34:12+05:30</t>
+    <t>2026-05-25T13:52:53+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T13:52:53+05:30</t>
+    <t>2026-05-25T14:14:21+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:14:21+05:30</t>
+    <t>2026-05-25T14:26:28+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:26:28+05:30</t>
+    <t>2026-05-25T14:41:34+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T14:41:34+05:30</t>
+    <t>2026-05-25T15:12:42+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:12:42+05:30</t>
+    <t>2026-05-25T15:24:41+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:24:41+05:30</t>
+    <t>2026-05-25T15:48:57+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:48:57+05:30</t>
+    <t>2026-05-25T16:36:06+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T16:36:06+05:30</t>
+    <t>2026-05-26T08:48:22+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T08:48:22+05:30</t>
+    <t>2026-05-26T12:06:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T12:06:33+05:30</t>
+    <t>2026-05-26T19:54:55+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T19:54:55+05:30</t>
+    <t>2026-06-10T16:33:40+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-period-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-period-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
